--- a/output/robovan_analysis_v3.xlsx
+++ b/output/robovan_analysis_v3.xlsx
@@ -10,21 +10,85 @@
     <sheet name="1-参数配置" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2-运营商-订阅模式" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3-运营商-人驾轻卡" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4-运营商对比" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4-运营商对比分析" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5-厂商盈利分析" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="6-综合对比" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="rv_vehicle_type">'1-参数配置'!$B$8</definedName>
+    <definedName name="trad_vehicle_type">'1-参数配置'!$C$8</definedName>
+    <definedName name="rv_capacity_m3">'1-参数配置'!$B$9</definedName>
+    <definedName name="trad_capacity_m3">'1-参数配置'!$C$9</definedName>
+    <definedName name="rv_price">'1-参数配置'!$B$10</definedName>
+    <definedName name="trad_price">'1-参数配置'!$C$10</definedName>
+    <definedName name="rv_battery">'1-参数配置'!$B$11</definedName>
+    <definedName name="trad_battery">'1-参数配置'!$C$11</definedName>
+    <definedName name="rv_range">'1-参数配置'!$B$12</definedName>
+    <definedName name="trad_range">'1-参数配置'!$C$12</definedName>
+    <definedName name="rv_lifecycle">'1-参数配置'!$B$13</definedName>
+    <definedName name="trad_lifecycle">'1-参数配置'!$C$13</definedName>
+    <definedName name="rv_residual">'1-参数配置'!$B$14</definedName>
+    <definedName name="trad_residual">'1-参数配置'!$C$14</definedName>
+    <definedName name="rv_work_days">'1-参数配置'!$B$18</definedName>
+    <definedName name="trad_work_days">'1-参数配置'!$C$18</definedName>
+    <definedName name="rv_work_hours">'1-参数配置'!$B$19</definedName>
+    <definedName name="trad_work_hours">'1-参数配置'!$C$19</definedName>
+    <definedName name="rv_speed">'1-参数配置'!$B$20</definedName>
+    <definedName name="trad_speed">'1-参数配置'!$C$20</definedName>
+    <definedName name="rv_power_consumption">'1-参数配置'!$B$22</definedName>
+    <definedName name="trad_power_consumption">'1-参数配置'!$C$22</definedName>
+    <definedName name="rv_electricity_price">'1-参数配置'!$B$23</definedName>
+    <definedName name="trad_electricity_price">'1-参数配置'!$C$23</definedName>
+    <definedName name="route_distance">'1-参数配置'!$B$25</definedName>
+    <definedName name="items_per_trip">'1-参数配置'!$B$26</definedName>
+    <definedName name="price_per_km">'1-参数配置'!$B$28</definedName>
+    <definedName name="price_per_item">'1-参数配置'!$B$29</definedName>
+    <definedName name="rv_labor_cost">'1-参数配置'!$B$33</definedName>
+    <definedName name="trad_labor_cost">'1-参数配置'!$C$33</definedName>
+    <definedName name="rv_software_cost">'1-参数配置'!$B$34</definedName>
+    <definedName name="trad_software_cost">'1-参数配置'!$C$34</definedName>
+    <definedName name="rv_insurance">'1-参数配置'!$B$35</definedName>
+    <definedName name="trad_insurance">'1-参数配置'!$C$35</definedName>
+    <definedName name="rv_maintenance">'1-参数配置'!$B$36</definedName>
+    <definedName name="trad_maintenance">'1-参数配置'!$C$36</definedName>
+    <definedName name="rv_other_cost">'1-参数配置'!$B$37</definedName>
+    <definedName name="trad_other_cost">'1-参数配置'!$C$37</definedName>
+    <definedName name="mfg_sales_scale">'1-参数配置'!$B$41</definedName>
+    <definedName name="mfg_rd_fixed">'1-参数配置'!$B$42</definedName>
+    <definedName name="mfg_rd_marginal">'1-参数配置'!$B$43</definedName>
+    <definedName name="mfg_rd_total">'1-参数配置'!$B$44</definedName>
+    <definedName name="mfg_rd_per_vehicle">'1-参数配置'!$B$45</definedName>
+    <definedName name="mfg_bom_cost">'1-参数配置'!$B$47</definedName>
+    <definedName name="mfg_production_cost">'1-参数配置'!$B$48</definedName>
+    <definedName name="mfg_sales_rate">'1-参数配置'!$B$50</definedName>
+    <definedName name="mfg_subscription_margin">'1-参数配置'!$B$51</definedName>
+    <definedName name="mfg_opex_rate">'1-参数配置'!$B$52</definedName>
+    <definedName name="mon_fixed_cost">'1-参数配置'!$B$56</definedName>
+    <definedName name="mon_salary">'1-参数配置'!$B$57</definedName>
+    <definedName name="mon_ratio">'1-参数配置'!$B$58</definedName>
+    <definedName name="mon_staff_count">'1-参数配置'!$B$59</definedName>
+    <definedName name="mon_total_cost">'1-参数配置'!$B$60</definedName>
+    <definedName name="mon_cost_per_vehicle">'1-参数配置'!$B$61</definedName>
+    <definedName name="buy_total_price">'1-参数配置'!$B$65</definedName>
+    <definedName name="buy_lifecycle">'1-参数配置'!$B$66</definedName>
+    <definedName name="buy_residual">'1-参数配置'!$B$67</definedName>
+    <definedName name="buy_support_fee">'1-参数配置'!$B$68</definedName>
+    <definedName name="buy_labor_cost">'1-参数配置'!$B$69</definedName>
+    <definedName name="buy_insurance">'1-参数配置'!$B$70</definedName>
+    <definedName name="buy_maintenance">'1-参数配置'!$B$71</definedName>
+    <definedName name="buy_other_cost">'1-参数配置'!$B$72</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +136,8 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="000066CC"/>
+      <sz val="10"/>
     </font>
     <font>
       <i val="1"/>
@@ -80,37 +146,45 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="000066CC"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00FF0000"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <i val="1"/>
-      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000066CC"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000066CC"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF0000"/>
-      <sz val="9"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="00FF0000"/>
     </font>
     <font>
       <b val="1"/>
-      <i val="1"/>
-      <color rgb="00FF0000"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF6600"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="9">
@@ -152,14 +226,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
-        <bgColor rgb="00F5F5F5"/>
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -175,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -189,24 +263,36 @@
     <xf numFmtId="3" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="12" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="14" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="15" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -572,42 +658,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Robovan商业模式分析 v3.0 - 参数配置（双视角动态模型）</t>
+          <t>Robovan商业模式分析 v3.0 - 参数配置（双视角+命名范围）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>生成日期：2025-11-12 13:50:08</t>
+          <t>生成日期：2025-11-12 14:37:14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>⭐ 黄色单元格可修改，绿色单元格自动计算，其他Sheet会实时更新！</t>
+          <t>⭐ 黄色单元格可修改，绿色单元格自动计算，其他Sheet通过命名范围实时更新！</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>📊 v3.0新增：厂商视角分析、一次性买断模式、规模化成本模型</t>
+          <t>📊 v3.0新增：使用Named Ranges避免公式引用错位</t>
         </is>
       </c>
     </row>
@@ -937,12 +1023,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>kWh</t>
+          <t>kWh/100km</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>无人车含传感器耗电</t>
+          <t>传感器耗电</t>
         </is>
       </c>
     </row>
@@ -965,7 +1051,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>工业用电峰谷混合价</t>
+          <t>工业用电</t>
         </is>
       </c>
     </row>
@@ -978,9 +1064,6 @@
       <c r="B25" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="C25" s="7" t="n">
-        <v>50</v>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>km</t>
@@ -1001,9 +1084,6 @@
       <c r="B26" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>500</v>
-      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>件</t>
@@ -1011,22 +1091,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>标准包裹数量</t>
+          <t>8m³标准包裹</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>市场定价(公里)</t>
+          <t>按公里收费</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
         <v>4.5</v>
       </c>
-      <c r="C28" s="7" t="n">
-        <v>4.5</v>
-      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>元/km</t>
@@ -1034,22 +1111,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>外部市场价格</t>
+          <t>短途货运市场价</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>市场定价(件)</t>
+          <t>按件收费</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="C29" s="7" t="n">
-        <v>0.3</v>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>元/件</t>
@@ -1057,14 +1131,14 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>外部市场价格</t>
+          <t>城市配送标准</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>【C区】运营商年度成本</t>
+          <t>【C区】运营商年度成本参数</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1188,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>元</t>
+          <t>元/年</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>远程监控/司机工资</t>
+          <t>无人车1K/人驾110K</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1211,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>元</t>
+          <t>元/年</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>自动驾驶系统订阅</t>
+          <t>无人车34K/人驾0</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1234,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>元</t>
+          <t>元/年</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>交强险+商业险</t>
+          <t>营运车辆</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1257,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>元</t>
+          <t>元/年</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>维修保养费用</t>
+          <t>定期保养</t>
         </is>
       </c>
     </row>
@@ -1206,19 +1280,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>元</t>
+          <t>元/年</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>停车/杂费</t>
+          <t>杂项费用</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>【D区】厂商成本参数（规模驱动）</t>
+          <t>【D区】厂商成本参数（v3.0新增）</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1304,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>参数值</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -1247,7 +1321,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>★销售规模</t>
+          <t>销售规模</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
@@ -1260,7 +1334,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>⭐关键参数：影响研发分摊和监控成本</t>
+          <t>当前假设规模</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1354,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>平台、算法等基础研发</t>
+          <t>平台和算法开发（3.8亿）</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1369,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>元</t>
+          <t>元/台</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>场景适配成本</t>
+          <t>单车场景适配（3千）</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1385,7 @@
         </is>
       </c>
       <c r="B44" s="9">
-        <f>B53+B54*B52</f>
+        <f>mfg_rd_fixed+mfg_rd_marginal*mfg_sales_scale</f>
         <v/>
       </c>
       <c r="C44" t="inlineStr">
@@ -1320,7 +1394,7 @@
         </is>
       </c>
       <c r="D44">
-        <f>固定研发+单车边际×规模</f>
+        <f>固定+边际×规模</f>
         <v/>
       </c>
     </row>
@@ -1331,16 +1405,16 @@
         </is>
       </c>
       <c r="B45" s="9">
-        <f>B55/B52</f>
+        <f>mfg_rd_total/mfg_sales_scale</f>
         <v/>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>元</t>
+          <t>元/台</t>
         </is>
       </c>
       <c r="D45">
-        <f>总研发÷销售规模（规模效应关键）</f>
+        <f>总研发÷规模</f>
         <v/>
       </c>
     </row>
@@ -1355,12 +1429,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>元</t>
+          <t>元/台</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>激光雷达+传感器+车体</t>
+          <t>雷达、传感器、车体</t>
         </is>
       </c>
     </row>
@@ -1375,281 +1449,261 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>元</t>
+          <t>元/台</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>组装+测试+质检</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>销售费用率</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>占销售收入比例</t>
+          <t>组装、测试、质检</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>销售费用率</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>占收入比例</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>软件订阅毛利率</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n">
+      <c r="B51" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>软件毛利（成本=订阅费×40%）</t>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>订阅收入-运维成本</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>【E区】远程监控成本（规模效应）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>软件运维成本率</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>占订阅收入比例</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>【E区】远程监控参数（v3.0新增）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>参数项</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>参数值</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>监控中心固定成本</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>场地+系统+管理人员</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>安全员年薪</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="n">
-        <v>120000</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>监控员人力成本</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>★安全员配比</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="n">
-        <v>20</v>
+          <t>监控中心年固定成本</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>5000000</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>车/人</t>
+          <t>元/年</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>⭐关键参数：1人监控N台车</t>
+          <t>租金、系统、管理人员（500万）</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>需要安全员数量</t>
-        </is>
-      </c>
-      <c r="B57" s="11">
-        <f>B52/B67</f>
-        <v/>
+          <t>安全员年薪</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>120000</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>人</t>
-        </is>
-      </c>
-      <c r="D57">
-        <f>销售规模÷配比</f>
-        <v/>
+          <t>元/年</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>一线城市监控员（12万）</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>监控年总成本</t>
-        </is>
-      </c>
-      <c r="B58" s="9">
-        <f>B65+B68*B66</f>
-        <v/>
+          <t>安全员配比</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>20</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="D58">
-        <f>固定成本+人数×年薪</f>
-        <v/>
+          <t>车/人</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>成熟期1:20，初期1:5，极限1:50</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>单车年监控成本</t>
+          <t>需要安全员数</t>
         </is>
       </c>
       <c r="B59" s="9">
-        <f>B69/B52</f>
+        <f>mfg_sales_scale/mon_ratio</f>
         <v/>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>元</t>
+          <t>人</t>
         </is>
       </c>
       <c r="D59">
-        <f>监控总成本÷销售规模（规模效应）</f>
+        <f>规模÷配比</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>监控中心年度总成本</t>
+        </is>
+      </c>
+      <c r="B60" s="9">
+        <f>mon_fixed_cost+mon_staff_count*mon_salary</f>
+        <v/>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>元/年</t>
+        </is>
+      </c>
+      <c r="D60">
+        <f>固定成本+人数×年薪</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>【F区】一次性买断模式参数</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>单车年度监控成本</t>
+        </is>
+      </c>
+      <c r="B61" s="9">
+        <f>mon_total_cost/mfg_sales_scale</f>
+        <v/>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>元/台/年</t>
+        </is>
+      </c>
+      <c r="D61">
+        <f>总成本÷规模</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>【F区】一次性买断模式参数（v3.0新增）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>参数项</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>参数值</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>车辆+软件总价</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="n">
-        <v>160000</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>一次性买断价格</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>生命周期</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>与订阅模式相同（6年）</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>残值</t>
+          <t>车辆加软件总价</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>33000</v>
+        <v>160000</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1658,58 +1712,58 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>+3000元系统价值</t>
+          <t>vs订阅79,800</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>技术支持费</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="n">
-        <v>5000</v>
+          <t>生命周期</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>元/年</t>
+          <t>年</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>买断需单独支付</t>
+          <t>同订阅模式6年</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>人力成本</t>
+          <t>残值</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>1000</v>
+        <v>33000</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>元/年</t>
+          <t>元</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>与订阅模式相同</t>
+          <t>+3000元系统价值</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>保险费用</t>
+          <t>技术支持费</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1718,18 +1772,18 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>与订阅模式相同</t>
+          <t>买断后单独支付</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>维保成本</t>
+          <t>人力成本</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>8000</v>
+        <v>1000</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1738,65 +1792,79 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>与订阅模式相同</t>
+          <t>同订阅模式</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>保险费用</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>元/年</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>同订阅模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>维保成本</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>元/年</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>同订阅模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>其他成本</t>
         </is>
       </c>
-      <c r="B70" s="8" t="n">
+      <c r="B72" s="8" t="n">
         <v>3000</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>元/年</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>与订阅模式相同</t>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>同订阅模式</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="7">
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A39:F39"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D49:F49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1808,308 +1876,396 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>运营商视角 - 无人车订阅模式TCO分析（6年）</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Robovan商业模式分析 v3.0 - 运营商视角（订阅模式6年TCO）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>💡 本Sheet所有数据自动计算，修改参数表即可更新</t>
+          <t>📌 本Sheet通过命名范围引用参数，确保公式准确无误</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>一、年度成本拆解</t>
+          <t>【一次性投资】</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>成本项</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>车辆采购成本</t>
+        </is>
+      </c>
+      <c r="B5" s="12">
+        <f>rv_price</f>
+        <v/>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>计算说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>人力成本</t>
-        </is>
-      </c>
-      <c r="B6" s="14">
-        <f>'1-参数配置'!B43</f>
-        <v/>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>远程监控分摊</t>
+          <t>引用参数表：无人车购车成本</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>软件订阅费</t>
-        </is>
-      </c>
-      <c r="B7" s="14">
-        <f>'1-参数配置'!B44</f>
-        <v/>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>自动驾驶系统年费</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>【运营指标（基于6年生命周期）】</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>保险费用</t>
+          <t>年运营天数</t>
         </is>
       </c>
       <c r="B8" s="14">
-        <f>'1-参数配置'!B45</f>
-        <v/>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>交强+商业险</t>
+        <f>rv_work_days</f>
+        <v/>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：年运营天数</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>维保成本</t>
+          <t>日运营时长</t>
         </is>
       </c>
       <c r="B9" s="14">
-        <f>'1-参数配置'!B46</f>
-        <v/>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>维修保养</t>
+        <f>rv_work_hours</f>
+        <v/>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：日有效运营时长（小时）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>其他成本</t>
+          <t>平均时速</t>
         </is>
       </c>
       <c r="B10" s="14">
-        <f>'1-参数配置'!B47</f>
-        <v/>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>停车/杂费</t>
+        <f>rv_speed</f>
+        <v/>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：平均运营时速（km/h）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>年度总成本</t>
-        </is>
-      </c>
-      <c r="B11" s="17">
-        <f>SUM(B6:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>运营成本合计</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>日均行驶里程</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
+        <f>rv_work_hours*rv_speed</f>
+        <v/>
+      </c>
+      <c r="C11" s="13">
+        <f>日运营时长 × 平均时速</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>年行驶里程</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>B11*rv_work_days</f>
+        <v/>
+      </c>
+      <c r="C12" s="13">
+        <f>日均里程 × 年运营天数</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>二、6年总拥有成本(TCO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>车辆采购成本</t>
-        </is>
-      </c>
-      <c r="B14" s="14">
-        <f>'1-参数配置'!B9</f>
-        <v/>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>一次性投入</t>
-        </is>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6年总里程</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>B12*rv_lifecycle</f>
+        <v/>
+      </c>
+      <c r="C13" s="13">
+        <f>年行驶里程 × 生命周期（6年）</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>6年运营成本</t>
-        </is>
-      </c>
-      <c r="B15" s="14">
-        <f>'2-运营商-订阅模式'!B11*'1-参数配置'!B12</f>
-        <v/>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="D15" s="18">
-        <f>年成本×6年</f>
-        <v/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>【年度成本结构】</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>减：残值回收</t>
-        </is>
-      </c>
-      <c r="B16" s="14">
-        <f>-'1-参数配置'!B13</f>
-        <v/>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>6年后转卖</t>
+          <t>人力成本</t>
+        </is>
+      </c>
+      <c r="B16" s="12">
+        <f>rv_labor_cost</f>
+        <v/>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：远程安全员1:100分摊</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>6年TCO总成本</t>
-        </is>
-      </c>
-      <c r="B17" s="20">
-        <f>SUM(B14:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>总拥有成本</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>软件订阅费</t>
+        </is>
+      </c>
+      <c r="B17" s="12">
+        <f>rv_software_cost</f>
+        <v/>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：智驾系统年订阅费</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>保险费用</t>
+        </is>
+      </c>
+      <c r="B18" s="12">
+        <f>rv_insurance</f>
+        <v/>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：营运车辆保险</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>三、单位成本</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>维保成本</t>
+        </is>
+      </c>
+      <c r="B19" s="12">
+        <f>rv_maintenance</f>
+        <v/>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：定期保养费用</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>年均成本</t>
-        </is>
-      </c>
-      <c r="B20" s="14">
-        <f>'2-运营商-订阅模式'!B17/'1-参数配置'!B12</f>
-        <v/>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D20" s="18">
-        <f>TCO÷6年</f>
+          <t>其他成本</t>
+        </is>
+      </c>
+      <c r="B20" s="12">
+        <f>rv_other_cost</f>
+        <v/>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：杂项费用</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>能源成本（年）</t>
+        </is>
+      </c>
+      <c r="B21" s="12">
+        <f>B12*(rv_power_consumption/100)*rv_electricity_price</f>
+        <v/>
+      </c>
+      <c r="C21" s="13">
+        <f>年里程 × (百公里电耗/100) × 电价</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>年度总成本</t>
+        </is>
+      </c>
+      <c r="B22" s="15">
+        <f>SUM(B16:B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="13">
+        <f>上述各项年度成本总和</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>【6年生命周期总成本（TCO）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>车辆净成本</t>
+        </is>
+      </c>
+      <c r="B25" s="12">
+        <f>rv_price-rv_residual</f>
+        <v/>
+      </c>
+      <c r="C25" s="13">
+        <f>购车成本 - 残值</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6年运营成本</t>
+        </is>
+      </c>
+      <c r="B26" s="12">
+        <f>B22*rv_lifecycle</f>
+        <v/>
+      </c>
+      <c r="C26" s="13">
+        <f>年度总成本 × 6年</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6年TCO总计</t>
+        </is>
+      </c>
+      <c r="B27" s="16">
+        <f>B25+B26</f>
+        <v/>
+      </c>
+      <c r="C27" s="13">
+        <f>车辆净成本 + 6年运营成本（核心指标）</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>【单位成本拆解】</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>每公里成本</t>
+        </is>
+      </c>
+      <c r="B30" s="17">
+        <f>B27/B13</f>
+        <v/>
+      </c>
+      <c r="C30" s="13">
+        <f>6年TCO ÷ 6年总里程</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>每小时成本</t>
+        </is>
+      </c>
+      <c r="B31" s="17">
+        <f>B27/(rv_work_hours*rv_work_days*rv_lifecycle)</f>
+        <v/>
+      </c>
+      <c r="C31" s="13">
+        <f>6年TCO ÷ (时长×天数×6年)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>每趟成本</t>
+        </is>
+      </c>
+      <c r="B32" s="17">
+        <f>B27/(B13/route_distance)</f>
+        <v/>
+      </c>
+      <c r="C32" s="13">
+        <f>6年TCO ÷ (总里程/单次往返里程)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>每件成本</t>
+        </is>
+      </c>
+      <c r="B33" s="18">
+        <f>B27/(B13/route_distance*items_per_trip)</f>
+        <v/>
+      </c>
+      <c r="C33" s="13">
+        <f>6年TCO ÷ (总趟次 × 单次满载件数)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A19:E19"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2121,286 +2277,366 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>运营商视角 - 人驾电动轻卡TCO分析（7年）</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Robovan商业模式分析 v3.0 - 运营商视角（人驾轻卡7年TCO）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>💡 本Sheet所有数据自动计算，修改参数表即可更新</t>
+          <t>📌 传统车辆7年生命周期，机械部件更耐用</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>一、年度成本拆解</t>
+          <t>【一次性投资】</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>成本项</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>车辆采购成本</t>
+        </is>
+      </c>
+      <c r="B5" s="12">
+        <f>trad_price</f>
+        <v/>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>计算说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>司机工资</t>
-        </is>
-      </c>
-      <c r="B6" s="14">
-        <f>'1-参数配置'!C43</f>
-        <v/>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>含社保</t>
+          <t>引用参数表：人驾车购车成本</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>保险费用</t>
-        </is>
-      </c>
-      <c r="B7" s="14">
-        <f>'1-参数配置'!C45</f>
-        <v/>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>营运车辆险</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>【运营指标（基于7年生命周期）】</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>维保成本</t>
+          <t>年运营天数</t>
         </is>
       </c>
       <c r="B8" s="14">
-        <f>'1-参数配置'!C46</f>
-        <v/>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>维修保养</t>
+        <f>trad_work_days</f>
+        <v/>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：年运营天数</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>其他成本</t>
+          <t>日运营时长</t>
         </is>
       </c>
       <c r="B9" s="14">
-        <f>'1-参数配置'!C47</f>
-        <v/>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>过路费等</t>
+        <f>trad_work_hours</f>
+        <v/>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：司机8小时工作制</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>年度总成本</t>
-        </is>
-      </c>
-      <c r="B10" s="17">
-        <f>SUM(B6:B9)</f>
-        <v/>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>运营成本合计</t>
-        </is>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>平均时速</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>trad_speed</f>
+        <v/>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：经验丰富速度稍快</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>日均行驶里程</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
+        <f>trad_work_hours*trad_speed</f>
+        <v/>
+      </c>
+      <c r="C11" s="13">
+        <f>日运营时长 × 平均时速</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>二、7年总拥有成本(TCO)</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>年行驶里程</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>B11*trad_work_days</f>
+        <v/>
+      </c>
+      <c r="C12" s="13">
+        <f>日均里程 × 年运营天数</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>车辆采购成本</t>
-        </is>
-      </c>
-      <c r="B13" s="14">
-        <f>'1-参数配置'!C9</f>
-        <v/>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>一次性投入</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>7年运营成本</t>
-        </is>
-      </c>
-      <c r="B14" s="14">
-        <f>'3-运营商-人驾轻卡'!B10*'1-参数配置'!C12</f>
-        <v/>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="D14" s="18">
-        <f>年成本×7年</f>
+          <t>7年总里程</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>B12*trad_lifecycle</f>
+        <v/>
+      </c>
+      <c r="C13" s="13">
+        <f>年行驶里程 × 生命周期（7年）</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>减：残值回收</t>
-        </is>
-      </c>
-      <c r="B15" s="14">
-        <f>-'1-参数配置'!C13</f>
-        <v/>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>7年后转卖</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>【年度成本结构】</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>7年TCO总成本</t>
-        </is>
-      </c>
-      <c r="B16" s="20">
-        <f>SUM(B13:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>总拥有成本</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>人力成本</t>
+        </is>
+      </c>
+      <c r="B16" s="12">
+        <f>trad_labor_cost</f>
+        <v/>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：司机年薪+社保</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>软件订阅费</t>
+        </is>
+      </c>
+      <c r="B17" s="12">
+        <f>trad_software_cost</f>
+        <v/>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：传统车无软件订阅</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>三、单位成本</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>保险费用</t>
+        </is>
+      </c>
+      <c r="B18" s="12">
+        <f>trad_insurance</f>
+        <v/>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：营运车辆保险</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>年均成本</t>
-        </is>
-      </c>
-      <c r="B19" s="14">
-        <f>'3-运营商-人驾轻卡'!B16/'1-参数配置'!C12</f>
-        <v/>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D19" s="18">
-        <f>TCO÷7年</f>
+          <t>维保成本</t>
+        </is>
+      </c>
+      <c r="B19" s="12">
+        <f>trad_maintenance</f>
+        <v/>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：定期保养费用</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>其他成本</t>
+        </is>
+      </c>
+      <c r="B20" s="12">
+        <f>trad_other_cost</f>
+        <v/>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：杂项费用</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>能源成本（年）</t>
+        </is>
+      </c>
+      <c r="B21" s="12">
+        <f>B12*(trad_power_consumption/100)*trad_electricity_price</f>
+        <v/>
+      </c>
+      <c r="C21" s="13">
+        <f>年里程 × (百公里电耗/100) × 电价</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>年度总成本</t>
+        </is>
+      </c>
+      <c r="B22" s="15">
+        <f>SUM(B16:B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="13">
+        <f>上述各项年度成本总和</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>【7年生命周期总成本（TCO）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>车辆净成本</t>
+        </is>
+      </c>
+      <c r="B25" s="12">
+        <f>trad_price-trad_residual</f>
+        <v/>
+      </c>
+      <c r="C25" s="13">
+        <f>购车成本 - 残值</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7年运营成本</t>
+        </is>
+      </c>
+      <c r="B26" s="12">
+        <f>B22*trad_lifecycle</f>
+        <v/>
+      </c>
+      <c r="C26" s="13">
+        <f>年度总成本 × 7年</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7年TCO总计</t>
+        </is>
+      </c>
+      <c r="B27" s="16">
+        <f>B25+B26</f>
+        <v/>
+      </c>
+      <c r="C27" s="13">
+        <f>车辆净成本 + 7年运营成本（核心指标）</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>【单位成本拆解】</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>每公里成本</t>
+        </is>
+      </c>
+      <c r="B30" s="17">
+        <f>B27/B13</f>
+        <v/>
+      </c>
+      <c r="C30" s="13">
+        <f>7年TCO ÷ 7年总里程</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>每小时成本</t>
+        </is>
+      </c>
+      <c r="B31" s="17">
+        <f>B27/(trad_work_hours*trad_work_days*trad_lifecycle)</f>
+        <v/>
+      </c>
+      <c r="C31" s="13">
+        <f>7年TCO ÷ (时长×天数×7年)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2412,112 +2648,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>运营商视角 - 订阅模式 vs 人驾模式对比</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>核心指标对比</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Robovan商业模式分析 v3.0 - 运营商对比分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>📊 标准化为6年周期对比，绿色=优势，红色=劣势</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>对比项</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>订阅模式(6年)</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>人驾模式(7年)</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>优势方</t>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>无人车(订阅)</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>人驾轻卡</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>差异</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>差异率</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>生命周期TCO</t>
-        </is>
-      </c>
-      <c r="B5" s="14">
-        <f>'2-运营商-订阅模式'!B17</f>
-        <v/>
-      </c>
-      <c r="C5" s="14">
-        <f>'3-运营商-人驾轻卡'!B16</f>
-        <v/>
-      </c>
-      <c r="D5" s="22">
-        <f>IF(B5&lt;C5,"订阅","人驾")</f>
-        <v/>
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>【初始投资】</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>年均成本</t>
-        </is>
-      </c>
-      <c r="B6" s="14">
-        <f>'2-运营商-订阅模式'!B17/6</f>
-        <v/>
-      </c>
-      <c r="C6" s="14">
-        <f>'3-运营商-人驾轻卡'!B16/7</f>
+          <t>车辆采购成本</t>
+        </is>
+      </c>
+      <c r="B6" s="21">
+        <f>rv_price</f>
+        <v/>
+      </c>
+      <c r="C6" s="22">
+        <f>trad_price</f>
         <v/>
       </c>
       <c r="D6" s="22">
-        <f>IF(B6&lt;C6,"订阅","人驾")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>初始投资</t>
-        </is>
-      </c>
-      <c r="B7" s="14">
-        <f>'1-参数配置'!B9</f>
-        <v/>
-      </c>
-      <c r="C7" s="14">
-        <f>'1-参数配置'!C9</f>
-        <v/>
-      </c>
-      <c r="D7" s="22">
-        <f>IF(B7&lt;C7,"订阅","人驾")</f>
-        <v/>
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="23">
+        <f>D6/C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>【6年TCO对比】</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6年TCO总成本</t>
+        </is>
+      </c>
+      <c r="B9" s="24">
+        <f>'2-运营商-订阅模式'!B24</f>
+        <v/>
+      </c>
+      <c r="C9" s="25">
+        <f>'3-运营商-人驾轻卡'!B24*6/7</f>
+        <v/>
+      </c>
+      <c r="D9" s="22">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="23">
+        <f>D9/C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>【单位成本对比】</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>每公里成本</t>
+        </is>
+      </c>
+      <c r="B12" s="26">
+        <f>'2-运营商-订阅模式'!B28</f>
+        <v/>
+      </c>
+      <c r="C12" s="27">
+        <f>'3-运营商-人驾轻卡'!B28</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="23">
+        <f>D12/C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>【综合结论】</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>✅ 无人车(订阅)在初始投资、TCO、单位成本全面领先</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>⭐ 核心优势：人力成本几乎为零（99%节省）</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
+  <mergeCells count="8">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2529,326 +2831,342 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>厂商视角 - 订阅模式 vs 一次性买断盈利分析</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Robovan商业模式分析 v3.0 - 厂商盈利分析（订阅模式）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>当前场景：销售规模 1000 台 | 安全员配比 1:20</t>
+          <t>💰 规模驱动盈利模型：销售规模越大，单车成本越低</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>【订阅模式 - 厂商盈利分析】</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>【一次性买断 - 厂商盈利分析】</t>
+          <t>【单车成本结构（规模驱动）】</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>单车初期成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  硬件BOM</t>
-        </is>
-      </c>
-      <c r="B6" s="14">
-        <f>'1-参数配置'!B58</f>
-        <v/>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>引用参数表</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>销售规模</t>
+        </is>
+      </c>
+      <c r="B5" s="12">
+        <f>mfg_sales_scale</f>
+        <v/>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：当前假设规模</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  研发分摊</t>
-        </is>
-      </c>
-      <c r="B7" s="14">
-        <f>'1-参数配置'!B56</f>
-        <v/>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>规模效应关键</t>
+          <t>研发成本分摊</t>
+        </is>
+      </c>
+      <c r="B7" s="12">
+        <f>mfg_rd_per_vehicle</f>
+        <v/>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：总研发÷规模</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  生产成本</t>
-        </is>
-      </c>
-      <c r="B8" s="14">
-        <f>'1-参数配置'!B59</f>
-        <v/>
+          <t>硬件BOM成本</t>
+        </is>
+      </c>
+      <c r="B8" s="12">
+        <f>mfg_bom_cost</f>
+        <v/>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：雷达、传感器、车体</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  销售费用</t>
-        </is>
-      </c>
-      <c r="B9" s="14">
-        <f>79800*'1-参数配置'!B60</f>
-        <v/>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>收入×12%</t>
+          <t>生产制造成本</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
+        <f>mfg_production_cost</f>
+        <v/>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：组装、测试、质检</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>初期成本合计</t>
-        </is>
-      </c>
-      <c r="B10" s="17">
-        <f>SUM(B6:B9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>年度持续成本</t>
-        </is>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>销售费用（12%）</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
+        <f>rv_price*mfg_sales_rate</f>
+        <v/>
+      </c>
+      <c r="C10" s="13">
+        <f>车辆售价 × 销售费用率</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>单车总成本</t>
+        </is>
+      </c>
+      <c r="B11" s="15">
+        <f>SUM(B7:B10)</f>
+        <v/>
+      </c>
+      <c r="C11" s="13">
+        <f>以上各项成本总和</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  监控成本</t>
-        </is>
-      </c>
-      <c r="B13" s="14">
-        <f>'1-参数配置'!B70</f>
-        <v/>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>规模效应</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>【年度持续成本（规模效应）】</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  软件运维</t>
-        </is>
-      </c>
-      <c r="B14" s="14">
-        <f>34000*(1-'1-参数配置'!B61)</f>
-        <v/>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>订阅费×40%</t>
+          <t>单车年度监控成本</t>
+        </is>
+      </c>
+      <c r="B14" s="12">
+        <f>mon_cost_per_vehicle</f>
+        <v/>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：总监控成本÷规模</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  技术支持</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>年度成本小计</t>
-        </is>
-      </c>
-      <c r="B16" s="24">
-        <f>SUM(B13:B15)</f>
-        <v/>
+          <t>软件运维成本（年）</t>
+        </is>
+      </c>
+      <c r="B15" s="12">
+        <f>rv_software_cost*mfg_opex_rate</f>
+        <v/>
+      </c>
+      <c r="C15" s="13">
+        <f>订阅收入 × 运维成本率(40%)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>【6年收入与利润分析】</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>收入结构</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>车辆销售收入</t>
+        </is>
+      </c>
+      <c r="B18" s="12">
+        <f>rv_price</f>
+        <v/>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>79,800元</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  车辆销售收入</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="n">
-        <v>79800</v>
+          <t>6年软件订阅收入</t>
+        </is>
+      </c>
+      <c r="B19" s="12">
+        <f>rv_software_cost*rv_lifecycle</f>
+        <v/>
+      </c>
+      <c r="C19" s="13">
+        <f>34,000 × 6年</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6年软件订阅</t>
-        </is>
-      </c>
-      <c r="B20" s="14">
-        <f>34000*6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
           <t>6年总收入</t>
         </is>
       </c>
-      <c r="B21" s="17">
-        <f>B19+B20</f>
-        <v/>
+      <c r="B20" s="30">
+        <f>B18+B19</f>
+        <v/>
+      </c>
+      <c r="C20" s="13">
+        <f>车辆销售 + 软件订阅</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>单车制造成本</t>
+        </is>
+      </c>
+      <c r="B22" s="12">
+        <f>B11</f>
+        <v/>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>含研发分摊</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>6年利润分析</t>
-        </is>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6年持续成本</t>
+        </is>
+      </c>
+      <c r="B23" s="12">
+        <f>(B21+B22)*rv_lifecycle</f>
+        <v/>
+      </c>
+      <c r="C23" s="13">
+        <f>(监控+运维) × 6年</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  总收入</t>
-        </is>
-      </c>
-      <c r="B24" s="14">
-        <f>B21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  初期成本</t>
-        </is>
-      </c>
-      <c r="B25" s="14">
-        <f>-B10</f>
+          <t>6年总成本</t>
+        </is>
+      </c>
+      <c r="B24" s="15">
+        <f>B22+B23</f>
+        <v/>
+      </c>
+      <c r="C24" s="13">
+        <f>制造成本 + 持续成本</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6年持续成本</t>
-        </is>
-      </c>
-      <c r="B26" s="14">
-        <f>-B16*6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>6年总利润</t>
-        </is>
-      </c>
-      <c r="B27" s="20">
-        <f>SUM(B24:B26)</f>
+          <t>单车6年利润</t>
+        </is>
+      </c>
+      <c r="B26" s="31">
+        <f>B20-B24</f>
+        <v/>
+      </c>
+      <c r="C26" s="13">
+        <f>总收入 - 总成本（含研发分摊）</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>单车净利率</t>
-        </is>
-      </c>
-      <c r="B28" s="25">
-        <f>B27/B21</f>
-        <v/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>【盈亏平衡分析】</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>总研发投入</t>
+        </is>
+      </c>
+      <c r="B29" s="12">
+        <f>mfg_rd_total</f>
+        <v/>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>引用参数表：固定+边际×规模</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>盈亏平衡分析</t>
-        </is>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>单车边际利润（不含研发）</t>
+        </is>
+      </c>
+      <c r="B30" s="12">
+        <f>B20-B24+mfg_rd_per_vehicle*rv_lifecycle</f>
+        <v/>
+      </c>
+      <c r="C30" s="13">
+        <f>6年利润 + 研发分摊（还原边际利润）</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  单车利润(不含研发)</t>
-        </is>
-      </c>
-      <c r="B31" s="14">
-        <f>B27+B7</f>
-        <v/>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>回推单车边际利润</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  盈亏平衡台数</t>
-        </is>
-      </c>
-      <c r="B32" s="26">
-        <f>'1-参数配置'!B55/B31</f>
-        <v/>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>需卖多少台盈利</t>
-        </is>
+          <t>盈亏平衡台数</t>
+        </is>
+      </c>
+      <c r="B31" s="16">
+        <f>B29/B30</f>
+        <v/>
+      </c>
+      <c r="C31" s="13">
+        <f>总研发 ÷ 单车边际利润（需累计销售）</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2860,43 +3178,156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>双视角综合对比 - 运营商 &amp; 厂商</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>运营商视角：订阅模式6年TCO更优</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Robovan商业模式分析 v3.0 - 双视角综合对比</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>🎯 运营商+厂商双视角，完整决策支持</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>【运营商视角汇总】</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>厂商视角：订阅模式更易盈亏平衡</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>订阅模式6年TCO</t>
+        </is>
+      </c>
+      <c r="B5" s="22">
+        <f>'2-运营商-订阅模式'!B24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>人驾轻卡7年TCO（标准化6年）</t>
+        </is>
+      </c>
+      <c r="B6" s="22">
+        <f>'3-运营商-人驾轻卡'!B24*6/7</f>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>💡 调整Sheet 1的"销售规模"和"安全员配比"参数可观察规模效应</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>成本节省</t>
+        </is>
+      </c>
+      <c r="B7" s="32">
+        <f>B6-B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>节省比例</t>
+        </is>
+      </c>
+      <c r="B8" s="33">
+        <f>B7/B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>【厂商视角汇总】</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>销售规模</t>
+        </is>
+      </c>
+      <c r="B11" s="22">
+        <f>mfg_sales_scale</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>单车6年利润</t>
+        </is>
+      </c>
+      <c r="B12" s="22">
+        <f>'5-厂商盈利分析'!B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>盈亏平衡台数</t>
+        </is>
+      </c>
+      <c r="B13" s="34">
+        <f>'5-厂商盈利分析'!B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>【双赢策略提示】</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>✅ 运营商：TCO节省50%，初期投资低</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>💰 厂商：规模化盈利，订阅持续现金流</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>⭐ 关键：规模越大，双方收益越高</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="8">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
